--- a/output/Data and Chart Outputs/panama_gas.xlsx
+++ b/output/Data and Chart Outputs/panama_gas.xlsx
@@ -160,6 +160,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -204,11 +205,23 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -231,11 +244,12 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>MMBtu/day</a:t>
+                  <a:t>mcm/d (1,030 Btu/cf)</a:t>
                 </a:r>
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -248,9 +262,6 @@
         </a:ln>
       </spPr>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -713,7 +724,7 @@
         <v>44197</v>
       </c>
       <c r="B2" t="n">
-        <v>27022</v>
+        <v>0.7428932754165063</v>
       </c>
     </row>
     <row r="3">
@@ -721,7 +732,7 @@
         <v>44228</v>
       </c>
       <c r="B3" t="n">
-        <v>44655</v>
+        <v>1.227662616154396</v>
       </c>
     </row>
     <row r="4">
@@ -729,7 +740,7 @@
         <v>44256</v>
       </c>
       <c r="B4" t="n">
-        <v>47130</v>
+        <v>1.295705723868697</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +748,7 @@
         <v>44287</v>
       </c>
       <c r="B5" t="n">
-        <v>36304</v>
+        <v>0.9980755484686864</v>
       </c>
     </row>
     <row r="6">
@@ -745,7 +756,7 @@
         <v>44317</v>
       </c>
       <c r="B6" t="n">
-        <v>22539</v>
+        <v>0.6196459009182383</v>
       </c>
     </row>
     <row r="7">
@@ -753,7 +764,7 @@
         <v>44348</v>
       </c>
       <c r="B7" t="n">
-        <v>14756</v>
+        <v>0.4056743828009017</v>
       </c>
     </row>
     <row r="8">
@@ -761,7 +772,7 @@
         <v>44378</v>
       </c>
       <c r="B8" t="n">
-        <v>24251</v>
+        <v>0.6667124869412218</v>
       </c>
     </row>
     <row r="9">
@@ -769,7 +780,7 @@
         <v>44409</v>
       </c>
       <c r="B9" t="n">
-        <v>10406</v>
+        <v>0.2860834662121295</v>
       </c>
     </row>
     <row r="10">
@@ -777,7 +788,7 @@
         <v>44440</v>
       </c>
       <c r="B10" t="n">
-        <v>7860</v>
+        <v>0.2160884148017815</v>
       </c>
     </row>
     <row r="11">
@@ -785,7 +796,7 @@
         <v>44470</v>
       </c>
       <c r="B11" t="n">
-        <v>24119</v>
+        <v>0.663083521196459</v>
       </c>
     </row>
     <row r="12">
@@ -793,7 +804,7 @@
         <v>44501</v>
       </c>
       <c r="B12" t="n">
-        <v>32388</v>
+        <v>0.8904162313740583</v>
       </c>
     </row>
     <row r="13">
@@ -801,7 +812,7 @@
         <v>44531</v>
       </c>
       <c r="B13" t="n">
-        <v>51490</v>
+        <v>1.4155715621048</v>
       </c>
     </row>
     <row r="14">
@@ -809,7 +820,7 @@
         <v>44562</v>
       </c>
       <c r="B14" t="n">
-        <v>49840</v>
+        <v>1.370209490295266</v>
       </c>
     </row>
     <row r="15">
@@ -817,7 +828,7 @@
         <v>44593</v>
       </c>
       <c r="B15" t="n">
-        <v>55172</v>
+        <v>1.516797712651894</v>
       </c>
     </row>
     <row r="16">
@@ -825,7 +836,7 @@
         <v>44621</v>
       </c>
       <c r="B16" t="n">
-        <v>52537</v>
+        <v>1.444355858580305</v>
       </c>
     </row>
     <row r="17">
@@ -833,7 +844,7 @@
         <v>44652</v>
       </c>
       <c r="B17" t="n">
-        <v>53663</v>
+        <v>1.47531203606972</v>
       </c>
     </row>
     <row r="18">
@@ -841,7 +852,7 @@
         <v>44682</v>
       </c>
       <c r="B18" t="n">
-        <v>16854</v>
+        <v>0.4633529444108429</v>
       </c>
     </row>
     <row r="19">
@@ -849,7 +860,7 @@
         <v>44713</v>
       </c>
       <c r="B19" t="n">
-        <v>1379</v>
+        <v>0.03791169516687744</v>
       </c>
     </row>
     <row r="20">
@@ -865,7 +876,7 @@
         <v>44774</v>
       </c>
       <c r="B21" t="n">
-        <v>1233</v>
+        <v>0.03389783911585198</v>
       </c>
     </row>
     <row r="22">
@@ -873,7 +884,7 @@
         <v>44805</v>
       </c>
       <c r="B22" t="n">
-        <v>76</v>
+        <v>0.002089404519711882</v>
       </c>
     </row>
     <row r="23">
@@ -881,7 +892,7 @@
         <v>44835</v>
       </c>
       <c r="B23" t="n">
-        <v>947</v>
+        <v>0.02603508000219937</v>
       </c>
     </row>
     <row r="24">
@@ -889,7 +900,7 @@
         <v>44866</v>
       </c>
       <c r="B24" t="n">
-        <v>32686</v>
+        <v>0.8986088964645076</v>
       </c>
     </row>
     <row r="25">
@@ -897,7 +908,7 @@
         <v>44896</v>
       </c>
       <c r="B25" t="n">
-        <v>46913</v>
+        <v>1.289739924121625</v>
       </c>
     </row>
     <row r="26">
@@ -905,7 +916,7 @@
         <v>44927</v>
       </c>
       <c r="B26" t="n">
-        <v>51020</v>
+        <v>1.402650244680266</v>
       </c>
     </row>
     <row r="27">
@@ -913,7 +924,7 @@
         <v>44958</v>
       </c>
       <c r="B27" t="n">
-        <v>55310</v>
+        <v>1.520591631385055</v>
       </c>
     </row>
     <row r="28">
@@ -921,7 +932,7 @@
         <v>44986</v>
       </c>
       <c r="B28" t="n">
-        <v>55406</v>
+        <v>1.523230879199428</v>
       </c>
     </row>
     <row r="29">
@@ -929,7 +940,7 @@
         <v>45017</v>
       </c>
       <c r="B29" t="n">
-        <v>51329</v>
+        <v>1.411145323582779</v>
       </c>
     </row>
     <row r="30">
@@ -937,7 +948,7 @@
         <v>45047</v>
       </c>
       <c r="B30" t="n">
-        <v>57221</v>
+        <v>1.573129158189916</v>
       </c>
     </row>
     <row r="31">
@@ -945,7 +956,7 @@
         <v>45078</v>
       </c>
       <c r="B31" t="n">
-        <v>53869</v>
+        <v>1.480975422004729</v>
       </c>
     </row>
     <row r="32">
@@ -953,7 +964,7 @@
         <v>45108</v>
       </c>
       <c r="B32" t="n">
-        <v>56469</v>
+        <v>1.552455050310662</v>
       </c>
     </row>
     <row r="33">
@@ -961,7 +972,7 @@
         <v>45139</v>
       </c>
       <c r="B33" t="n">
-        <v>55379</v>
+        <v>1.522488590751636</v>
       </c>
     </row>
     <row r="34">
@@ -969,7 +980,7 @@
         <v>45170</v>
       </c>
       <c r="B34" t="n">
-        <v>51526</v>
+        <v>1.41656128003519</v>
       </c>
     </row>
     <row r="35">
@@ -977,7 +988,7 @@
         <v>45200</v>
       </c>
       <c r="B35" t="n">
-        <v>30354</v>
+        <v>0.8344971683070325</v>
       </c>
     </row>
     <row r="36">
@@ -985,7 +996,7 @@
         <v>45231</v>
       </c>
       <c r="B36" t="n">
-        <v>47604</v>
+        <v>1.308737009952164</v>
       </c>
     </row>
     <row r="37">
@@ -993,7 +1004,7 @@
         <v>45261</v>
       </c>
       <c r="B37" t="n">
-        <v>43238</v>
+        <v>1.188706218727663</v>
       </c>
     </row>
     <row r="38">
@@ -1001,7 +1012,7 @@
         <v>45292</v>
       </c>
       <c r="B38" t="n">
-        <v>56524</v>
+        <v>1.553967119370979</v>
       </c>
     </row>
     <row r="39">
@@ -1009,7 +1020,7 @@
         <v>45323</v>
       </c>
       <c r="B39" t="n">
-        <v>50373</v>
+        <v>1.384862814097982</v>
       </c>
     </row>
     <row r="40">
@@ -1017,7 +1028,7 @@
         <v>45352</v>
       </c>
       <c r="B40" t="n">
-        <v>43139</v>
+        <v>1.18598449441909</v>
       </c>
     </row>
     <row r="41">
@@ -1025,7 +1036,7 @@
         <v>45383</v>
       </c>
       <c r="B41" t="n">
-        <v>54363</v>
+        <v>1.494556551382856</v>
       </c>
     </row>
     <row r="42">
@@ -1033,7 +1044,7 @@
         <v>45413</v>
       </c>
       <c r="B42" t="n">
-        <v>54394</v>
+        <v>1.49540880848958</v>
       </c>
     </row>
     <row r="43">
@@ -1041,7 +1052,7 @@
         <v>45444</v>
       </c>
       <c r="B43" t="n">
-        <v>48084</v>
+        <v>1.321933249024028</v>
       </c>
     </row>
     <row r="44">
@@ -1049,7 +1060,7 @@
         <v>45474</v>
       </c>
       <c r="B44" t="n">
-        <v>39491</v>
+        <v>1.08569307747292</v>
       </c>
     </row>
     <row r="45">
@@ -1057,7 +1068,7 @@
         <v>45505</v>
       </c>
       <c r="B45" t="n">
-        <v>41888</v>
+        <v>1.151591796338044</v>
       </c>
     </row>
     <row r="46">
@@ -1065,7 +1076,7 @@
         <v>45536</v>
       </c>
       <c r="B46" t="n">
-        <v>42335</v>
+        <v>1.163880793973717</v>
       </c>
     </row>
     <row r="47">
@@ -1073,7 +1084,7 @@
         <v>45566</v>
       </c>
       <c r="B47" t="n">
-        <v>46457</v>
+        <v>1.277203497003354</v>
       </c>
     </row>
     <row r="48">
@@ -1081,7 +1092,7 @@
         <v>45597</v>
       </c>
       <c r="B48" t="n">
-        <v>7278</v>
+        <v>0.2000879749271458</v>
       </c>
     </row>
     <row r="49">
@@ -1089,7 +1100,7 @@
         <v>45627</v>
       </c>
       <c r="B49" t="n">
-        <v>12439</v>
+        <v>0.3419750371144224</v>
       </c>
     </row>
     <row r="50">
@@ -1097,7 +1108,7 @@
         <v>45658</v>
       </c>
       <c r="B50" t="n">
-        <v>26810</v>
+        <v>0.7370649364930995</v>
       </c>
     </row>
     <row r="51">
@@ -1105,7 +1116,7 @@
         <v>45689</v>
       </c>
       <c r="B51" t="n">
-        <v>67505</v>
+        <v>1.855858580304613</v>
       </c>
     </row>
     <row r="52">
@@ -1113,7 +1124,7 @@
         <v>45717</v>
       </c>
       <c r="B52" t="n">
-        <v>84913</v>
+        <v>2.334442183977566</v>
       </c>
     </row>
     <row r="53">
@@ -1121,7 +1132,7 @@
         <v>45748</v>
       </c>
       <c r="B53" t="n">
-        <v>90828</v>
+        <v>2.497058338373563</v>
       </c>
     </row>
     <row r="54">
@@ -1129,7 +1140,7 @@
         <v>45778</v>
       </c>
       <c r="B54" t="n">
-        <v>62532</v>
+        <v>1.71914004508715</v>
       </c>
     </row>
     <row r="55">
@@ -1137,7 +1148,7 @@
         <v>45809</v>
       </c>
       <c r="B55" t="n">
-        <v>72217</v>
+        <v>1.98540166052675</v>
       </c>
     </row>
     <row r="56">
@@ -1145,7 +1156,7 @@
         <v>45839</v>
       </c>
       <c r="B56" t="n">
-        <v>42679</v>
+        <v>1.173338098641887</v>
       </c>
     </row>
     <row r="57">
@@ -1153,7 +1164,7 @@
         <v>45870</v>
       </c>
       <c r="B57" t="n">
-        <v>49918</v>
+        <v>1.372353879144444</v>
       </c>
     </row>
     <row r="58">
@@ -1161,7 +1172,7 @@
         <v>45901</v>
       </c>
       <c r="B58" t="n">
-        <v>62564</v>
+        <v>1.720019794358608</v>
       </c>
     </row>
     <row r="59">
@@ -1169,7 +1180,7 @@
         <v>45931</v>
       </c>
       <c r="B59" t="n">
-        <v>48532</v>
+        <v>1.334249738824435</v>
       </c>
     </row>
     <row r="60">
@@ -1177,7 +1188,7 @@
         <v>45962</v>
       </c>
       <c r="B60" t="n">
-        <v>45238</v>
+        <v>1.243690548193765</v>
       </c>
     </row>
     <row r="61">
@@ -1185,7 +1196,7 @@
         <v>45992</v>
       </c>
       <c r="B61" t="n">
-        <v>47283</v>
+        <v>1.299912025072854</v>
       </c>
     </row>
     <row r="62">
@@ -1193,7 +1204,7 @@
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>48110</v>
+        <v>1.322648045307087</v>
       </c>
     </row>
     <row r="63">
@@ -1201,7 +1212,7 @@
         <v>46054</v>
       </c>
       <c r="B63" t="n">
-        <v>21373</v>
+        <v>0.5875900368395007</v>
       </c>
     </row>
     <row r="64">
@@ -1209,7 +1220,7 @@
         <v>46082</v>
       </c>
       <c r="B64" t="n">
-        <v>46076</v>
+        <v>1.266728982240062</v>
       </c>
     </row>
     <row r="65">
@@ -1217,7 +1228,7 @@
         <v>46113</v>
       </c>
       <c r="B65" t="n">
-        <v>67976</v>
+        <v>1.86880738989388</v>
       </c>
     </row>
     <row r="66">
@@ -1225,7 +1236,7 @@
         <v>46143</v>
       </c>
       <c r="B66" t="n">
-        <v>78272</v>
+        <v>2.151866717985374</v>
       </c>
     </row>
     <row r="67">
@@ -1233,7 +1244,7 @@
         <v>46174</v>
       </c>
       <c r="B67" t="n">
-        <v>78687</v>
+        <v>2.16327596634959</v>
       </c>
     </row>
     <row r="68">
@@ -1241,7 +1252,7 @@
         <v>46204</v>
       </c>
       <c r="B68" t="n">
-        <v>87289</v>
+        <v>2.399763567383296</v>
       </c>
     </row>
     <row r="69">
@@ -1249,7 +1260,7 @@
         <v>46235</v>
       </c>
       <c r="B69" t="n">
-        <v>90331</v>
+        <v>2.483394732501237</v>
       </c>
     </row>
     <row r="70">
@@ -1257,7 +1268,7 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>78196</v>
+        <v>2.115302138890416</v>
       </c>
     </row>
   </sheetData>
@@ -3717,10 +3728,10 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>323956.3</v>
+        <v>329751.9</v>
       </c>
       <c r="C70" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D70" t="n">
         <v>30</v>
@@ -3729,19 +3740,19 @@
         <v>7</v>
       </c>
       <c r="F70" t="n">
-        <v>2345890</v>
+        <v>2308263</v>
       </c>
       <c r="G70" t="n">
-        <v>78196</v>
+        <v>76942</v>
       </c>
       <c r="H70" t="n">
-        <v>75.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="I70" t="n">
-        <v>64.63</v>
+        <v>63.59</v>
       </c>
       <c r="J70" t="n">
-        <v>45.1</v>
+        <v>44.4</v>
       </c>
       <c r="K70" t="b">
         <v>1</v>

--- a/output/Data and Chart Outputs/panama_gas.xlsx
+++ b/output/Data and Chart Outputs/panama_gas.xlsx
@@ -155,7 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Panama LNG use for power (estimate from CND gas generation) (to Sep/26)</a:t>
+              <a:t>Panama LNG use for power (estimate from CND gas generation) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -185,12 +185,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$70</f>
+              <f>'Chart'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$70</f>
+              <f>'Chart'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -635,7 +635,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jan 2021 to Sep 2026 (follows panama_power_generation_daily.xlsx).</t>
+          <t>Jan 2021 to Oct 2026 (follows panama_power_generation_daily.xlsx).</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B70"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1269,6 +1269,14 @@
       </c>
       <c r="B70" t="n">
         <v>2.115302138890416</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1.027629625556716</v>
       </c>
     </row>
   </sheetData>
@@ -1283,7 +1291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3758,6 +3766,41 @@
         <v>1</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B71" t="n">
+        <v>5339.8</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>31</v>
+      </c>
+      <c r="E71" t="n">
+        <v>7</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1158737</v>
+      </c>
+      <c r="G71" t="n">
+        <v>37379</v>
+      </c>
+      <c r="H71" t="n">
+        <v>36</v>
+      </c>
+      <c r="I71" t="n">
+        <v>31.92</v>
+      </c>
+      <c r="J71" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="K71" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/Data and Chart Outputs/panama_gas.xlsx
+++ b/output/Data and Chart Outputs/panama_gas.xlsx
@@ -155,6 +155,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Panama LNG use for power (estimate from CND gas generation) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -1276,7 +1277,7 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>1.027629625556716</v>
+        <v>0.7523230879199428</v>
       </c>
     </row>
   </sheetData>
@@ -3771,10 +3772,10 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>5339.8</v>
+        <v>101642.7</v>
       </c>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D71" t="n">
         <v>31</v>
@@ -3783,19 +3784,19 @@
         <v>7</v>
       </c>
       <c r="F71" t="n">
-        <v>1158737</v>
+        <v>848326</v>
       </c>
       <c r="G71" t="n">
-        <v>37379</v>
+        <v>27365</v>
       </c>
       <c r="H71" t="n">
-        <v>36</v>
+        <v>26.4</v>
       </c>
       <c r="I71" t="n">
-        <v>31.92</v>
+        <v>23.37</v>
       </c>
       <c r="J71" t="n">
-        <v>22.3</v>
+        <v>16.3</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>

--- a/output/Data and Chart Outputs/panama_gas.xlsx
+++ b/output/Data and Chart Outputs/panama_gas.xlsx
@@ -1277,7 +1277,7 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>0.7523230879199428</v>
+        <v>0.733545939407269</v>
       </c>
     </row>
   </sheetData>
@@ -3772,10 +3772,10 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>101642.7</v>
+        <v>102915.1</v>
       </c>
       <c r="C71" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D71" t="n">
         <v>31</v>
@@ -3784,19 +3784,19 @@
         <v>7</v>
       </c>
       <c r="F71" t="n">
-        <v>848326</v>
+        <v>827132</v>
       </c>
       <c r="G71" t="n">
-        <v>27365</v>
+        <v>26682</v>
       </c>
       <c r="H71" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="I71" t="n">
-        <v>23.37</v>
+        <v>22.79</v>
       </c>
       <c r="J71" t="n">
-        <v>16.3</v>
+        <v>15.9</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>

--- a/output/Data and Chart Outputs/panama_gas.xlsx
+++ b/output/Data and Chart Outputs/panama_gas.xlsx
@@ -1277,7 +1277,7 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>0.733545939407269</v>
+        <v>0.7146313300709298</v>
       </c>
     </row>
   </sheetData>
@@ -3772,10 +3772,10 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>102915.1</v>
+        <v>103976.8</v>
       </c>
       <c r="C71" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D71" t="n">
         <v>31</v>
@@ -3784,19 +3784,19 @@
         <v>7</v>
       </c>
       <c r="F71" t="n">
-        <v>827132</v>
+        <v>805820</v>
       </c>
       <c r="G71" t="n">
-        <v>26682</v>
+        <v>25994</v>
       </c>
       <c r="H71" t="n">
-        <v>25.7</v>
+        <v>25.1</v>
       </c>
       <c r="I71" t="n">
-        <v>22.79</v>
+        <v>22.2</v>
       </c>
       <c r="J71" t="n">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>

--- a/output/Data and Chart Outputs/panama_gas.xlsx
+++ b/output/Data and Chart Outputs/panama_gas.xlsx
@@ -1277,7 +1277,7 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>0.7146313300709298</v>
+        <v>0.7038544014955738</v>
       </c>
     </row>
   </sheetData>
@@ -3772,10 +3772,10 @@
         <v>46296</v>
       </c>
       <c r="B71" t="n">
-        <v>103976.8</v>
+        <v>106066.5</v>
       </c>
       <c r="C71" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D71" t="n">
         <v>31</v>
@@ -3784,19 +3784,19 @@
         <v>7</v>
       </c>
       <c r="F71" t="n">
-        <v>805820</v>
+        <v>793670</v>
       </c>
       <c r="G71" t="n">
-        <v>25994</v>
+        <v>25602</v>
       </c>
       <c r="H71" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="I71" t="n">
-        <v>22.2</v>
+        <v>21.86</v>
       </c>
       <c r="J71" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="K71" t="b">
         <v>0</v>
